--- a/data/dividends_info_20260420.xlsx
+++ b/data/dividends_info_20260420.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37.20999908447266</v>
+        <v>37.27500152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2418704708798449</v>
+        <v>0.2414486822690422</v>
       </c>
       <c r="J2" t="n">
         <v>329</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>56.65000152587891</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.23565751305448</v>
+        <v>1.245551584514583</v>
       </c>
       <c r="J3" t="n">
         <v>308</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J4" t="n">
         <v>238</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37.20999908447266</v>
+        <v>37.27500152587891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2418704708798449</v>
+        <v>0.2414486822690422</v>
       </c>
       <c r="J6" t="n">
         <v>238</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.115000009536743</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.640661922118176</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>217</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.75</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I9" t="n">
-        <v>1.043478260869565</v>
+        <v>1.052631614170798</v>
       </c>
       <c r="J9" t="n">
         <v>182</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>37.20999908447266</v>
+        <v>37.27500152587891</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2418704708798449</v>
+        <v>0.2414486822690422</v>
       </c>
       <c r="J11" t="n">
         <v>154</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.059999942779541</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I13" t="n">
-        <v>4.125412580207591</v>
+        <v>4.084967396648271</v>
       </c>
       <c r="J13" t="n">
         <v>98</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.72700023651123</v>
+        <v>9.730999946594238</v>
       </c>
       <c r="I14" t="n">
-        <v>2.672972074412675</v>
+        <v>2.671873408970654</v>
       </c>
       <c r="J14" t="n">
         <v>91</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.6200008392334</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="I15" t="n">
-        <v>3.610108120955276</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J15" t="n">
         <v>91</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.904000043869019</v>
+        <v>3.946000099182129</v>
       </c>
       <c r="I16" t="n">
-        <v>5.635245838316418</v>
+        <v>5.575265952111823</v>
       </c>
       <c r="J16" t="n">
         <v>91</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6.184999942779541</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>3.880355735171501</v>
+        <v>3.902438963875515</v>
       </c>
       <c r="J18" t="n">
         <v>91</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.739999771118164</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I20" t="n">
-        <v>2.090592417856904</v>
+        <v>2.158273403506726</v>
       </c>
       <c r="J20" t="n">
         <v>84</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.850000381469727</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5076141935391424</v>
+        <v>0.5319149152031317</v>
       </c>
       <c r="J21" t="n">
         <v>84</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.200000047683716</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I22" t="n">
-        <v>3.863636279894303</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J22" t="n">
         <v>77</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.590000152587891</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I23" t="n">
-        <v>1.525054415532715</v>
+        <v>1.518438133897318</v>
       </c>
       <c r="J23" t="n">
         <v>77</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>35.54999923706055</v>
+        <v>34.79999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4219409373253273</v>
+        <v>0.4310344922084259</v>
       </c>
       <c r="J24" t="n">
         <v>77</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.75</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6611570039494726</v>
       </c>
       <c r="J25" t="n">
         <v>70</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22.54000091552734</v>
+        <v>22.81999969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>4.214729198815446</v>
+        <v>4.163014954883932</v>
       </c>
       <c r="J26" t="n">
         <v>63</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.79999923706055</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7276119610120848</v>
+        <v>0.7456979076275785</v>
       </c>
       <c r="J27" t="n">
         <v>63</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.889999985694885</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I28" t="n">
-        <v>1.746031759247188</v>
+        <v>1.709844606054362</v>
       </c>
       <c r="J28" t="n">
         <v>63</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.175000190734863</v>
+        <v>5.164999961853027</v>
       </c>
       <c r="I29" t="n">
-        <v>5.603864527758002</v>
+        <v>5.614714465476158</v>
       </c>
       <c r="J29" t="n">
         <v>63</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.093999862670898</v>
+        <v>4.118000030517578</v>
       </c>
       <c r="I30" t="n">
-        <v>3.90815841150559</v>
+        <v>3.885381224241761</v>
       </c>
       <c r="J30" t="n">
         <v>63</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.584000110626221</v>
+        <v>2.582000017166138</v>
       </c>
       <c r="I31" t="n">
-        <v>5.36377686014924</v>
+        <v>5.367931800098119</v>
       </c>
       <c r="J31" t="n">
         <v>63</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>57.68999862670898</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>1.092043707743002</v>
+        <v>1.084337377875517</v>
       </c>
       <c r="J32" t="n">
         <v>63</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.21999979019165</v>
+        <v>5.304999828338623</v>
       </c>
       <c r="I33" t="n">
-        <v>2.681992444962531</v>
+        <v>2.639019878042938</v>
       </c>
       <c r="J33" t="n">
         <v>63</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>19.20000076293945</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="I34" t="n">
-        <v>4.06249983857076</v>
+        <v>4.30939217437002</v>
       </c>
       <c r="J34" t="n">
         <v>63</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>22.46999931335449</v>
+        <v>22.38999938964844</v>
       </c>
       <c r="I35" t="n">
-        <v>3.78282165542757</v>
+        <v>3.796337754225131</v>
       </c>
       <c r="J35" t="n">
         <v>63</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>37.20999908447266</v>
+        <v>37.27500152587891</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2418704708798449</v>
+        <v>0.2414486822690422</v>
       </c>
       <c r="J36" t="n">
         <v>63</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.527999877929688</v>
+        <v>6.627999782562256</v>
       </c>
       <c r="I37" t="n">
-        <v>2.777267208796243</v>
+        <v>2.735365207418775</v>
       </c>
       <c r="J37" t="n">
         <v>63</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.579999923706055</v>
+        <v>8.420000076293945</v>
       </c>
       <c r="I38" t="n">
-        <v>3.030303057248692</v>
+        <v>3.087885957768765</v>
       </c>
       <c r="J38" t="n">
         <v>63</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9.98799991607666</v>
+        <v>10.08500003814697</v>
       </c>
       <c r="I39" t="n">
-        <v>2.773328016894969</v>
+        <v>2.746653435322111</v>
       </c>
       <c r="J39" t="n">
         <v>63</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.230000019073486</v>
+        <v>1.235000014305115</v>
       </c>
       <c r="I40" t="n">
-        <v>1.097560958589989</v>
+        <v>1.093117396245207</v>
       </c>
       <c r="J40" t="n">
         <v>56</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.138000011444092</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I41" t="n">
-        <v>2.658289021164402</v>
+        <v>2.682926891674109</v>
       </c>
       <c r="J41" t="n">
         <v>56</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.35000038146973</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I43" t="n">
-        <v>3.915343862660136</v>
+        <v>3.901581617691721</v>
       </c>
       <c r="J43" t="n">
         <v>45</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9070000052452087</v>
+        <v>0.8980000019073486</v>
       </c>
       <c r="I44" t="n">
-        <v>3.307607478115665</v>
+        <v>3.340757231211593</v>
       </c>
       <c r="J44" t="n">
         <v>42</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="I46" t="n">
-        <v>3.157894736842105</v>
+        <v>3.116883116883117</v>
       </c>
       <c r="J46" t="n">
         <v>42</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="I47" t="n">
-        <v>2.222222222222222</v>
+        <v>2.262443399861825</v>
       </c>
       <c r="J47" t="n">
         <v>42</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.714999914169312</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I48" t="n">
-        <v>6.629834463736007</v>
+        <v>6.617646989216029</v>
       </c>
       <c r="J48" t="n">
         <v>35</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8.949999809265137</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I49" t="n">
-        <v>3.35195537869662</v>
+        <v>3.448275937667407</v>
       </c>
       <c r="J49" t="n">
         <v>35</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13.72999954223633</v>
+        <v>13.36999988555908</v>
       </c>
       <c r="I50" t="n">
-        <v>1.820830359323379</v>
+        <v>1.869857906805404</v>
       </c>
       <c r="J50" t="n">
         <v>35</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.349999904632568</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8955224135533352</v>
+        <v>0.8797653737504787</v>
       </c>
       <c r="J51" t="n">
         <v>35</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13.30000019073486</v>
+        <v>13.55000019073486</v>
       </c>
       <c r="I53" t="n">
-        <v>4.360902193099543</v>
+        <v>4.280442744174932</v>
       </c>
       <c r="J53" t="n">
         <v>35</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2.394000053405762</v>
+        <v>2.413000106811523</v>
       </c>
       <c r="I54" t="n">
-        <v>4.344193720967011</v>
+        <v>4.309987376561824</v>
       </c>
       <c r="J54" t="n">
         <v>28</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10.11999988555908</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="I55" t="n">
-        <v>2.865612680626813</v>
+        <v>2.897102830859719</v>
       </c>
       <c r="J55" t="n">
         <v>28</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.115000009536743</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I56" t="n">
-        <v>3.640661922118176</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J56" t="n">
         <v>28</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>37.5099983215332</v>
+        <v>37.45000076293945</v>
       </c>
       <c r="I57" t="n">
-        <v>4.372167617662974</v>
+        <v>4.379172140426083</v>
       </c>
       <c r="J57" t="n">
         <v>28</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>37.41999816894531</v>
+        <v>37.04999923706055</v>
       </c>
       <c r="I58" t="n">
-        <v>5.344735697127295</v>
+        <v>5.398110772427306</v>
       </c>
       <c r="J58" t="n">
         <v>28</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>4.105999946594238</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>2.435460333674529</v>
+        <v>2.450980437988963</v>
       </c>
       <c r="J59" t="n">
         <v>28</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>36.75</v>
+        <v>36.88000106811523</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4039727891156463</v>
+        <v>0.4025487952828498</v>
       </c>
       <c r="J60" t="n">
         <v>28</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>23.70000076293945</v>
+        <v>23.28000068664551</v>
       </c>
       <c r="I61" t="n">
-        <v>3.88185641512146</v>
+        <v>3.951889917802944</v>
       </c>
       <c r="J61" t="n">
         <v>28</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.595000267028809</v>
+        <v>8.534999847412109</v>
       </c>
       <c r="I62" t="n">
-        <v>3.490401287721036</v>
+        <v>3.514938551416175</v>
       </c>
       <c r="J62" t="n">
         <v>28</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>87.83999633789062</v>
+        <v>86.69999694824219</v>
       </c>
       <c r="I63" t="n">
-        <v>1.183970905462556</v>
+        <v>1.19953868120763</v>
       </c>
       <c r="J63" t="n">
         <v>28</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>50.34000015258789</v>
+        <v>48.88000106811523</v>
       </c>
       <c r="I64" t="n">
-        <v>1.390544294553432</v>
+        <v>1.432078528444662</v>
       </c>
       <c r="J64" t="n">
         <v>28</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>56.65000152587891</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="I65" t="n">
-        <v>3.883495041028365</v>
+        <v>3.914590694188689</v>
       </c>
       <c r="J65" t="n">
         <v>28</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9.16100025177002</v>
+        <v>9.133999824523926</v>
       </c>
       <c r="I66" t="n">
-        <v>9.387621180709358</v>
+        <v>9.415371321674227</v>
       </c>
       <c r="J66" t="n">
         <v>28</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>12.39999961853027</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="I67" t="n">
-        <v>4.516129171190852</v>
+        <v>4.534412815405569</v>
       </c>
       <c r="J67" t="n">
         <v>28</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2.130000114440918</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I68" t="n">
-        <v>1.877934171402577</v>
+        <v>1.904761991262981</v>
       </c>
       <c r="J68" t="n">
         <v>28</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>9.359999656677246</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I69" t="n">
-        <v>3.205128322691611</v>
+        <v>3.267973747570104</v>
       </c>
       <c r="J69" t="n">
         <v>28</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>74.5</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="I71" t="n">
-        <v>2.76510067114094</v>
+        <v>2.791327797852894</v>
       </c>
       <c r="J71" t="n">
         <v>28</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15.85000038146973</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="I72" t="n">
-        <v>4.731861084854148</v>
+        <v>4.820051283896272</v>
       </c>
       <c r="J72" t="n">
         <v>28</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>16.40999984741211</v>
+        <v>16.23999977111816</v>
       </c>
       <c r="I73" t="n">
-        <v>1.828153581898483</v>
+        <v>1.847290666429266</v>
       </c>
       <c r="J73" t="n">
         <v>28</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I74" t="n">
-        <v>1.847826086956522</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="J74" t="n">
         <v>28</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>34.70000076293945</v>
+        <v>34.13999938964844</v>
       </c>
       <c r="I75" t="n">
-        <v>2.449567669484962</v>
+        <v>2.489748140586458</v>
       </c>
       <c r="J75" t="n">
         <v>28</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>63.27999877929688</v>
+        <v>63.06000137329102</v>
       </c>
       <c r="I76" t="n">
-        <v>2.054361607265576</v>
+        <v>2.061528657927707</v>
       </c>
       <c r="J76" t="n">
         <v>28</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I77" t="n">
-        <v>7.5</v>
+        <v>7.444168346935813</v>
       </c>
       <c r="J77" t="n">
         <v>28</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>6</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I78" t="n">
-        <v>7.833333333333332</v>
+        <v>7.343749890569598</v>
       </c>
       <c r="J78" t="n">
         <v>28</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>20.95999908447266</v>
+        <v>21</v>
       </c>
       <c r="I80" t="n">
-        <v>4.770992574807927</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J80" t="n">
         <v>28</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4.849999904632568</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I81" t="n">
-        <v>4.432989777889247</v>
+        <v>4.405737601599046</v>
       </c>
       <c r="J81" t="n">
         <v>28</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>21.76000022888184</v>
+        <v>22.30500030517578</v>
       </c>
       <c r="I82" t="n">
-        <v>1.240808810478006</v>
+        <v>1.21049090475622</v>
       </c>
       <c r="J82" t="n">
         <v>28</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8.100000381469727</v>
+        <v>8</v>
       </c>
       <c r="I83" t="n">
-        <v>2.469135686185122</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>28</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>9.550000190734863</v>
+        <v>9.5</v>
       </c>
       <c r="I84" t="n">
-        <v>2.513088955043594</v>
+        <v>2.526315789473684</v>
       </c>
       <c r="J84" t="n">
         <v>28</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.43000030517578</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="I85" t="n">
-        <v>3.52206861012706</v>
+        <v>3.584391865625737</v>
       </c>
       <c r="J85" t="n">
         <v>28</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.800000190734863</v>
+        <v>4.820000171661377</v>
       </c>
       <c r="I86" t="n">
-        <v>1.93749992301067</v>
+        <v>1.929460512196297</v>
       </c>
       <c r="J86" t="n">
         <v>28</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.75</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I87" t="n">
-        <v>1.043478260869565</v>
+        <v>1.052631614170798</v>
       </c>
       <c r="J87" t="n">
         <v>28</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>38.68000030517578</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9048603858288139</v>
+        <v>0.9186352073943854</v>
       </c>
       <c r="J88" t="n">
         <v>28</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>7.385000228881836</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I89" t="n">
-        <v>7.505754675974149</v>
+        <v>7.572404194004189</v>
       </c>
       <c r="J89" t="n">
         <v>28</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2.220000028610229</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I90" t="n">
-        <v>2.702702667871647</v>
+        <v>2.71493207983419</v>
       </c>
       <c r="J90" t="n">
         <v>28</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>12.94999980926514</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I91" t="n">
-        <v>1.544401567148357</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J91" t="n">
         <v>28</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.199999809265137</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="I92" t="n">
-        <v>1.661290373688063</v>
+        <v>1.655948608911872</v>
       </c>
       <c r="J92" t="n">
         <v>28</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5.922999858856201</v>
+        <v>5.798999786376953</v>
       </c>
       <c r="I93" t="n">
-        <v>3.207833944414295</v>
+        <v>3.276427090864</v>
       </c>
       <c r="J93" t="n">
         <v>28</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.34500026702881</v>
+        <v>10.48499965667725</v>
       </c>
       <c r="I94" t="n">
-        <v>4.175930293369387</v>
+        <v>4.1201718087314</v>
       </c>
       <c r="J94" t="n">
         <v>28</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>27.77000045776367</v>
+        <v>26.45999908447266</v>
       </c>
       <c r="I95" t="n">
-        <v>1.584443618102242</v>
+        <v>1.66288743470971</v>
       </c>
       <c r="J95" t="n">
         <v>28</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.110000014305115</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I96" t="n">
-        <v>2.702702667871647</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J96" t="n">
         <v>28</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>8.550000190734863</v>
+        <v>8.5</v>
       </c>
       <c r="I97" t="n">
-        <v>5.497075900762102</v>
+        <v>5.529411764705882</v>
       </c>
       <c r="J97" t="n">
         <v>28</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>56.79999923706055</v>
+        <v>57.2400016784668</v>
       </c>
       <c r="I98" t="n">
-        <v>2.464788765501489</v>
+        <v>2.445841996763372</v>
       </c>
       <c r="J98" t="n">
         <v>28</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.611000061035156</v>
+        <v>3.746999979019165</v>
       </c>
       <c r="I99" t="n">
-        <v>8.307947796433982</v>
+        <v>8.006405168930094</v>
       </c>
       <c r="J99" t="n">
         <v>28</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3.420000076293945</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I101" t="n">
-        <v>4.970760123029561</v>
+        <v>4.885057444489921</v>
       </c>
       <c r="J101" t="n">
         <v>28</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>20.70000076293945</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I102" t="n">
-        <v>3.381642387440174</v>
+        <v>3.39805818950212</v>
       </c>
       <c r="J102" t="n">
         <v>28</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.619999885559082</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="I103" t="n">
-        <v>1.33587792094622</v>
+        <v>1.315789431227401</v>
       </c>
       <c r="J103" t="n">
         <v>28</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>6.130000114440918</v>
+        <v>6.090000152587891</v>
       </c>
       <c r="I104" t="n">
-        <v>5.383360421520929</v>
+        <v>5.418719076054038</v>
       </c>
       <c r="J104" t="n">
         <v>28</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9750000238418579</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I105" t="n">
-        <v>7.179487003925837</v>
+        <v>7.007006916704271</v>
       </c>
       <c r="J105" t="n">
         <v>28</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.40000152587891</v>
+        <v>50.15000152587891</v>
       </c>
       <c r="I106" t="n">
-        <v>1.408730116080326</v>
+        <v>1.415752698698561</v>
       </c>
       <c r="J106" t="n">
         <v>28</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>96</v>
+        <v>93.69999694824219</v>
       </c>
       <c r="I107" t="n">
-        <v>1.40625</v>
+        <v>1.440768456743612</v>
       </c>
       <c r="J107" t="n">
         <v>28</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.119999885559082</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I108" t="n">
-        <v>1.123595523677711</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J108" t="n">
         <v>28</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.872999906539917</v>
+        <v>3.996000051498413</v>
       </c>
       <c r="I110" t="n">
-        <v>4.389362357405156</v>
+        <v>4.254254199427593</v>
       </c>
       <c r="J110" t="n">
         <v>28</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>58.5</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7745266984825121</v>
       </c>
       <c r="J112" t="n">
         <v>28</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>4.860000133514404</v>
+        <v>4.820000171661377</v>
       </c>
       <c r="I113" t="n">
-        <v>0.823045244878931</v>
+        <v>0.829875489116687</v>
       </c>
       <c r="J113" t="n">
         <v>28</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>35.47999954223633</v>
+        <v>34.22000122070312</v>
       </c>
       <c r="I114" t="n">
-        <v>2.95941379241015</v>
+        <v>3.068380954249497</v>
       </c>
       <c r="J114" t="n">
         <v>28</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1.620000004768372</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I115" t="n">
-        <v>3.086419744001731</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J115" t="n">
         <v>28</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>19.98999977111816</v>
+        <v>19.65999984741211</v>
       </c>
       <c r="I116" t="n">
-        <v>1.900950497003153</v>
+        <v>1.93285861113585</v>
       </c>
       <c r="J116" t="n">
         <v>28</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>24.42000007629395</v>
+        <v>25.3799991607666</v>
       </c>
       <c r="I117" t="n">
-        <v>2.457002449326191</v>
+        <v>2.36406627202535</v>
       </c>
       <c r="J117" t="n">
         <v>28</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>35.65000152587891</v>
+        <v>35.5</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9817671389044105</v>
+        <v>0.9859154929577464</v>
       </c>
       <c r="J118" t="n">
         <v>28</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.519999980926514</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I119" t="n">
-        <v>0.482954548071485</v>
+        <v>0.488505744448992</v>
       </c>
       <c r="J119" t="n">
         <v>28</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.869999885559082</v>
+        <v>2.934999942779541</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3484320696428174</v>
+        <v>0.3407155091979209</v>
       </c>
       <c r="J120" t="n">
         <v>28</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>22.54999923706055</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="I121" t="n">
-        <v>4.966740744537582</v>
+        <v>4.982206507147382</v>
       </c>
       <c r="J121" t="n">
         <v>28</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1.570000052452087</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I122" t="n">
-        <v>6.369426538796359</v>
+        <v>6.578947450975964</v>
       </c>
       <c r="J122" t="n">
         <v>28</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>2.696000099182129</v>
+        <v>2.598000049591064</v>
       </c>
       <c r="I123" t="n">
-        <v>9.643916559160173</v>
+        <v>10.0076980383786</v>
       </c>
       <c r="J123" t="n">
         <v>28</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.444000005722046</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="I124" t="n">
-        <v>3.776595735838848</v>
+        <v>3.67729085062525</v>
       </c>
       <c r="J124" t="n">
         <v>28</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9.359999656677246</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>3.739316376473546</v>
+        <v>3.820960762339775</v>
       </c>
       <c r="J125" t="n">
         <v>21</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>4.980000019073486</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I126" t="n">
-        <v>1.927710835990328</v>
+        <v>1.761467951554743</v>
       </c>
       <c r="J126" t="n">
         <v>21</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.199999809265137</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J129" t="n">
         <v>21</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>16.54000091552734</v>
+        <v>16.31999969482422</v>
       </c>
       <c r="I131" t="n">
-        <v>3.022974439684658</v>
+        <v>3.063725547486203</v>
       </c>
       <c r="J131" t="n">
         <v>21</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.700000047683716</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I133" t="n">
-        <v>4.074074002123338</v>
+        <v>3.900709312198738</v>
       </c>
       <c r="J133" t="n">
         <v>21</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.050000190734863</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9392264995421837</v>
+        <v>0.9659090699735757</v>
       </c>
       <c r="J134" t="n">
         <v>21</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1.350000023841858</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="I136" t="n">
-        <v>2.222222182976366</v>
+        <v>2.127659624835675</v>
       </c>
       <c r="J136" t="n">
         <v>21</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>7.320000171661377</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="I139" t="n">
-        <v>3.005464410393148</v>
+        <v>3.05131759828037</v>
       </c>
       <c r="J139" t="n">
         <v>21</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>3.464999914169312</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I140" t="n">
-        <v>4.617604731986203</v>
+        <v>4.692081993335886</v>
       </c>
       <c r="J140" t="n">
         <v>14</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>22.39999961853027</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="I141" t="n">
-        <v>2.723214332090349</v>
+        <v>2.779043183588078</v>
       </c>
       <c r="J141" t="n">
         <v>14</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.039999961853027</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
-        <v>4.934210588231972</v>
+        <v>5</v>
       </c>
       <c r="J142" t="n">
         <v>14</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12.60000038146973</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="I143" t="n">
-        <v>5.555555387359032</v>
+        <v>5.511811106401145</v>
       </c>
       <c r="J143" t="n">
         <v>14</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.550000190734863</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="I144" t="n">
-        <v>5.345549631457311</v>
+        <v>5.459892825370714</v>
       </c>
       <c r="J144" t="n">
         <v>14</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.664999961853027</v>
+        <v>7.764999866485596</v>
       </c>
       <c r="I145" t="n">
-        <v>3.522504909898617</v>
+        <v>3.47714107717301</v>
       </c>
       <c r="J145" t="n">
         <v>14</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>5.949999809265137</v>
+        <v>5.864999771118164</v>
       </c>
       <c r="I146" t="n">
-        <v>5.882353129742826</v>
+        <v>5.967604665963566</v>
       </c>
       <c r="J146" t="n">
         <v>14</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>37</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="I147" t="n">
-        <v>2.972972972972973</v>
+        <v>3.005464606174182</v>
       </c>
       <c r="J147" t="n">
         <v>14</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>18.85000038146973</v>
+        <v>18.75</v>
       </c>
       <c r="I148" t="n">
-        <v>3.97877976032976</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>14</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>4.394999980926514</v>
+        <v>4.34499979019165</v>
       </c>
       <c r="I150" t="n">
-        <v>3.412969298088105</v>
+        <v>3.452244125272645</v>
       </c>
       <c r="J150" t="n">
         <v>14</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>12.34000015258789</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="I151" t="n">
-        <v>1.597803870031967</v>
+        <v>1.610857873259486</v>
       </c>
       <c r="J151" t="n">
         <v>14</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="I152" t="n">
-        <v>3.666666666666667</v>
+        <v>3.697478991596639</v>
       </c>
       <c r="J152" t="n">
         <v>14</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>46.59999847412109</v>
+        <v>46.29999923706055</v>
       </c>
       <c r="I153" t="n">
-        <v>1.008583724012374</v>
+        <v>1.015118807224064</v>
       </c>
       <c r="J153" t="n">
         <v>14</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>23.39999961853027</v>
+        <v>24.14999961853027</v>
       </c>
       <c r="I155" t="n">
-        <v>1.153846172656299</v>
+        <v>1.118012440020203</v>
       </c>
       <c r="J155" t="n">
         <v>14</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>10.5</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I156" t="n">
-        <v>3.619047619047619</v>
+        <v>3.601895669478002</v>
       </c>
       <c r="J156" t="n">
         <v>14</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>30.39999961853027</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9868421176463945</v>
+        <v>1.010100984153337</v>
       </c>
       <c r="J157" t="n">
         <v>14</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.2000000029802322</v>
+        <v>0.2014999985694885</v>
       </c>
       <c r="I158" t="n">
-        <v>3.499999947845937</v>
+        <v>3.473945434091905</v>
       </c>
       <c r="J158" t="n">
         <v>7</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>7.570000171661377</v>
+        <v>7.610000133514404</v>
       </c>
       <c r="I159" t="n">
-        <v>2.113606292889754</v>
+        <v>2.10249667796142</v>
       </c>
       <c r="J159" t="n">
         <v>7</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.239999771118164</v>
+        <v>8.130000114440918</v>
       </c>
       <c r="I161" t="n">
-        <v>3.033980666798916</v>
+        <v>3.075030707022222</v>
       </c>
       <c r="J161" t="n">
         <v>7</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1.450000047683716</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="I162" t="n">
-        <v>4.827586048139834</v>
+        <v>4.861110917947919</v>
       </c>
       <c r="J162" t="n">
         <v>7</v>
@@ -8089,8 +8089,12 @@
           <t>IT0004998065</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>6.420000076293945</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7.788161901216574</v>
+      </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
@@ -8132,8 +8136,12 @@
           <t>IT0004776628</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>18.69499969482422</v>
+      </c>
+      <c r="I164" t="n">
+        <v>3.476865528807443</v>
+      </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
@@ -8175,8 +8183,12 @@
           <t>IT0005218380</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
+      <c r="H165" t="n">
+        <v>12.71500015258789</v>
+      </c>
+      <c r="I165" t="n">
+        <v>4.246952367437397</v>
+      </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
@@ -8218,8 +8230,12 @@
           <t>NL0015435975</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>6.438000202178955</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1.553277366567258</v>
+      </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
@@ -8261,8 +8277,12 @@
           <t>IT0005215329</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="H167" t="n">
+        <v>9.100000381469727</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1.758241684536706</v>
+      </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
@@ -8304,8 +8324,12 @@
           <t>NL0011585146</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
+      <c r="H168" t="n">
+        <v>311.9500122070312</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1.158839512274435</v>
+      </c>
       <c r="J168" t="n">
         <v>0</v>
       </c>
@@ -8347,8 +8371,12 @@
           <t>IT0005144784</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>28.79999923706055</v>
+      </c>
+      <c r="I169" t="n">
+        <v>4.722222347318394</v>
+      </c>
       <c r="J169" t="n">
         <v>0</v>
       </c>
@@ -8390,8 +8418,12 @@
           <t>NL0015000LU4</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
+      <c r="H170" t="n">
+        <v>13.98999977111816</v>
+      </c>
+      <c r="I170" t="n">
+        <v>41.61258109537984</v>
+      </c>
       <c r="J170" t="n">
         <v>0</v>
       </c>
@@ -8433,8 +8465,12 @@
           <t>IT0004931058</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
+      <c r="H171" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3.982300998709326</v>
+      </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
@@ -8476,8 +8512,12 @@
           <t>IT0000062957</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>19.94499969482422</v>
+      </c>
+      <c r="I172" t="n">
+        <v>3.158686435896445</v>
+      </c>
       <c r="J172" t="n">
         <v>0</v>
       </c>
@@ -8519,8 +8559,12 @@
           <t>IT0004176001</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+      <c r="H173" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.7475082961743593</v>
+      </c>
       <c r="J173" t="n">
         <v>0</v>
       </c>
@@ -8562,8 +8606,12 @@
           <t>IT0005239360</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>67.98999786376953</v>
+      </c>
+      <c r="I174" t="n">
+        <v>2.53096051488035</v>
+      </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
@@ -8606,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>25.79999923706055</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5426356749611693</v>
+        <v>0.5468749918509277</v>
       </c>
       <c r="J175" t="n">
         <v>-7</v>
@@ -8653,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1.529999971389771</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="I176" t="n">
-        <v>3.92156870078234</v>
+        <v>3.614457904003342</v>
       </c>
       <c r="J176" t="n">
         <v>-7</v>
@@ -8700,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>2.160000085830688</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I177" t="n">
-        <v>1.574074011525993</v>
+        <v>1.588784968845712</v>
       </c>
       <c r="J177" t="n">
         <v>-21</v>
@@ -8747,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>21.76000022888184</v>
+        <v>22.30500030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>1.19485292860845</v>
+        <v>1.165657908283768</v>
       </c>
       <c r="J178" t="n">
         <v>-28</v>
@@ -8794,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>37.20999908447266</v>
+        <v>37.27500152587891</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2418704708798449</v>
+        <v>0.2414486822690422</v>
       </c>
       <c r="J179" t="n">
         <v>-28</v>
@@ -8817,7 +8865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C635"/>
+  <dimension ref="A1:C645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9588,7 +9636,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9605,7 +9653,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9758,7 +9806,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9775,7 +9823,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9785,14 +9833,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9802,14 +9850,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9826,7 +9874,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9843,7 +9891,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9877,7 +9925,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9894,7 +9942,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9962,7 +10010,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9979,7 +10027,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10098,7 +10146,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10183,7 +10231,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10217,7 +10265,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10285,7 +10333,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10295,14 +10343,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10312,14 +10360,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10329,14 +10377,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10346,14 +10394,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10370,7 +10418,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10380,14 +10428,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10404,7 +10452,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10414,14 +10462,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10438,7 +10486,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10448,14 +10496,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10465,14 +10513,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10489,7 +10537,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10499,14 +10547,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10523,7 +10571,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10540,7 +10588,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10557,7 +10605,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10574,7 +10622,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10591,7 +10639,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10601,14 +10649,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10625,7 +10673,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10642,7 +10690,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10659,7 +10707,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10669,14 +10717,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10693,7 +10741,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10710,7 +10758,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10727,7 +10775,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10744,7 +10792,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,7 +10809,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10771,14 +10819,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10795,7 +10843,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10812,7 +10860,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10822,14 +10870,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10839,14 +10887,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10863,7 +10911,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10880,7 +10928,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10897,7 +10945,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10931,7 +10979,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10948,7 +10996,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10965,7 +11013,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10982,7 +11030,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10999,7 +11047,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,7 +11064,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11033,7 +11081,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11050,7 +11098,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11067,7 +11115,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11084,7 +11132,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11101,7 +11149,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11118,7 +11166,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11135,7 +11183,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11152,7 +11200,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11162,14 +11210,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11186,7 +11234,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11203,7 +11251,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11220,7 +11268,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11237,7 +11285,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11254,7 +11302,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11271,7 +11319,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11288,7 +11336,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11305,7 +11353,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11315,14 +11363,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11339,7 +11387,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11349,14 +11397,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11373,7 +11421,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11383,14 +11431,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11407,7 +11455,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11417,14 +11465,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11441,7 +11489,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11458,7 +11506,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11475,7 +11523,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11492,7 +11540,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11509,7 +11557,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11526,7 +11574,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11543,7 +11591,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11560,7 +11608,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11577,7 +11625,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11594,7 +11642,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11611,7 +11659,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11628,7 +11676,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11645,7 +11693,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11662,7 +11710,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11679,7 +11727,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11689,14 +11737,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11713,7 +11761,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11730,7 +11778,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11747,7 +11795,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11764,7 +11812,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11781,7 +11829,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11798,7 +11846,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11815,7 +11863,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11832,7 +11880,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11849,7 +11897,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11866,7 +11914,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11876,14 +11924,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11900,7 +11948,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11917,7 +11965,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11934,7 +11982,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11944,7 +11992,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11968,7 +12016,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11985,7 +12033,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11995,14 +12043,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12012,14 +12060,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12036,7 +12084,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12053,7 +12101,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12070,7 +12118,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12087,7 +12135,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12097,14 +12145,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12121,7 +12169,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12138,7 +12186,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12155,7 +12203,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12172,7 +12220,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12189,7 +12237,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12206,7 +12254,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12223,7 +12271,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12240,7 +12288,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12257,7 +12305,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12267,14 +12315,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12291,7 +12339,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12301,14 +12349,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12342,7 +12390,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12359,7 +12407,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12376,7 +12424,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12393,7 +12441,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12403,14 +12451,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12427,7 +12475,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12437,14 +12485,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12461,7 +12509,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12495,7 +12543,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12512,7 +12560,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12529,7 +12577,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12539,14 +12587,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12563,7 +12611,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12580,7 +12628,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12597,7 +12645,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12614,7 +12662,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12624,14 +12672,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12648,7 +12696,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12665,7 +12713,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12682,7 +12730,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12692,7 +12740,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12764,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12726,14 +12774,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12767,7 +12815,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12777,14 +12825,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12801,7 +12849,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12818,7 +12866,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12835,7 +12883,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12852,7 +12900,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12869,7 +12917,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12886,7 +12934,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12903,7 +12951,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12920,7 +12968,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12930,14 +12978,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12947,14 +12995,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12971,7 +13019,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12981,14 +13029,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13005,7 +13053,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13022,7 +13070,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13039,7 +13087,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13056,7 +13104,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13073,7 +13121,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13090,7 +13138,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13107,7 +13155,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13124,7 +13172,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13141,7 +13189,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13158,7 +13206,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13168,14 +13216,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13192,7 +13240,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13202,14 +13250,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13226,7 +13274,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13243,7 +13291,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13260,7 +13308,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13270,14 +13318,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13294,7 +13342,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13311,7 +13359,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13328,7 +13376,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13345,7 +13393,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13362,7 +13410,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13372,14 +13420,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13396,7 +13444,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13406,14 +13454,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13423,14 +13471,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13447,7 +13495,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13464,7 +13512,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13481,7 +13529,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13498,7 +13546,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13515,7 +13563,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13532,7 +13580,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13549,7 +13597,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13566,7 +13614,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13576,14 +13624,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13600,7 +13648,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13617,7 +13665,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13627,14 +13675,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13651,7 +13699,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13668,7 +13716,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13678,14 +13726,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13695,14 +13743,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13719,7 +13767,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13736,7 +13784,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13753,7 +13801,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13763,14 +13811,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13787,7 +13835,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13804,7 +13852,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13821,7 +13869,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13838,7 +13886,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13848,14 +13896,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13872,7 +13920,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13882,14 +13930,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13906,7 +13954,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13923,7 +13971,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13933,14 +13981,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13957,7 +14005,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13967,14 +14015,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13984,14 +14032,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14008,7 +14056,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14025,7 +14073,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14042,7 +14090,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14059,7 +14107,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14076,7 +14124,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14093,7 +14141,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14110,7 +14158,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14127,7 +14175,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14144,7 +14192,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14161,7 +14209,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14178,7 +14226,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14195,7 +14243,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14212,7 +14260,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14229,7 +14277,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14239,14 +14287,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14263,7 +14311,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14273,14 +14321,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14297,7 +14345,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14314,7 +14362,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14331,7 +14379,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14341,14 +14389,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14358,14 +14406,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14375,14 +14423,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14399,7 +14447,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14416,7 +14464,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14433,7 +14481,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14450,7 +14498,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14467,7 +14515,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14484,7 +14532,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14501,7 +14549,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14518,7 +14566,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14535,7 +14583,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14552,7 +14600,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14569,7 +14617,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14586,7 +14634,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14596,14 +14644,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14613,14 +14661,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14637,7 +14685,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14654,7 +14702,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14664,14 +14712,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14688,7 +14736,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14705,12 +14753,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14727,7 +14775,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -14739,12 +14787,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -14756,29 +14804,29 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -14790,12 +14838,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -14807,12 +14855,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -14824,12 +14872,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -14841,29 +14889,29 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -14875,12 +14923,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -14892,7 +14940,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14902,14 +14950,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14919,14 +14967,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14936,14 +14984,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14960,7 +15008,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14977,7 +15025,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14994,7 +15042,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -15004,14 +15052,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15028,7 +15076,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15045,7 +15093,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15062,29 +15110,29 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15096,12 +15144,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15113,12 +15161,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -15130,46 +15178,46 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -15181,29 +15229,29 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15215,12 +15263,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -15232,7 +15280,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15249,7 +15297,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15266,7 +15314,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15276,14 +15324,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15300,7 +15348,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15310,14 +15358,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15334,7 +15382,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15351,7 +15399,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15361,14 +15409,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15378,14 +15426,14 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15395,14 +15443,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15436,7 +15484,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15453,7 +15501,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15470,7 +15518,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15480,14 +15528,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15497,14 +15545,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15514,87 +15562,87 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -15606,12 +15654,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -15623,29 +15671,29 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -15657,12 +15705,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -15674,24 +15722,24 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15701,14 +15749,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15725,7 +15773,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15742,7 +15790,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15752,14 +15800,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15769,14 +15817,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15786,14 +15834,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15803,14 +15851,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15827,7 +15875,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15837,14 +15885,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15861,7 +15909,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15878,7 +15926,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15888,14 +15936,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15905,14 +15953,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15922,7 +15970,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -15946,46 +15994,46 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15997,29 +16045,29 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -16031,29 +16079,29 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -16065,12 +16113,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -16082,12 +16130,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -16099,12 +16147,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -16116,7 +16164,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16126,7 +16174,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16198,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16167,7 +16215,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16177,14 +16225,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16194,14 +16242,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16211,14 +16259,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16235,7 +16283,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16245,14 +16293,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16269,7 +16317,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16286,7 +16334,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16303,7 +16351,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16313,14 +16361,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16330,14 +16378,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16347,14 +16395,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16364,14 +16412,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16381,14 +16429,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16398,14 +16446,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16422,7 +16470,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16432,14 +16480,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16449,14 +16497,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16466,14 +16514,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16483,14 +16531,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16507,7 +16555,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16517,14 +16565,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16534,14 +16582,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16551,14 +16599,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16568,14 +16616,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16592,7 +16640,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16602,14 +16650,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16619,14 +16667,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16636,14 +16684,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16653,14 +16701,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16670,14 +16718,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16687,14 +16735,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16711,29 +16759,29 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -16745,46 +16793,46 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -16796,12 +16844,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16813,29 +16861,29 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16847,29 +16895,29 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -16881,7 +16929,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16898,12 +16946,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16915,12 +16963,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16932,46 +16980,46 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -16983,46 +17031,46 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -17034,29 +17082,29 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -17068,12 +17116,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -17085,29 +17133,29 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17119,46 +17167,46 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17170,46 +17218,46 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17221,24 +17269,24 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17248,14 +17296,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17265,14 +17313,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17289,7 +17337,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17299,14 +17347,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17323,7 +17371,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17333,14 +17381,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17357,7 +17405,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17374,7 +17422,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17384,14 +17432,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17408,7 +17456,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17418,14 +17466,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17442,7 +17490,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17459,7 +17507,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17469,14 +17517,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17493,7 +17541,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17510,7 +17558,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17520,19 +17568,19 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -17544,29 +17592,29 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -17578,29 +17626,29 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -17612,63 +17660,63 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -17680,12 +17728,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -17697,7 +17745,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17707,14 +17755,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17724,14 +17772,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17741,14 +17789,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17758,14 +17806,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17782,7 +17830,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17799,7 +17847,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17816,7 +17864,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17833,7 +17881,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17860,14 +17908,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17877,14 +17925,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17901,7 +17949,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17918,7 +17966,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17928,14 +17976,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17952,7 +18000,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17969,7 +18017,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17979,14 +18027,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18003,7 +18051,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18020,7 +18068,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18030,14 +18078,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -18047,14 +18095,14 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18071,7 +18119,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18122,7 +18170,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18132,36 +18180,36 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -18173,46 +18221,46 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -18224,29 +18272,29 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -18258,12 +18306,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -18275,12 +18323,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -18292,17 +18340,17 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18343,7 +18391,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18360,7 +18408,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18370,14 +18418,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18394,7 +18442,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18404,14 +18452,14 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18428,7 +18476,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18445,7 +18493,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18455,14 +18503,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18479,7 +18527,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18496,7 +18544,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18513,7 +18561,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18530,7 +18578,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18540,14 +18588,14 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18564,7 +18612,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18581,7 +18629,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18598,7 +18646,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18615,7 +18663,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18625,14 +18673,14 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18642,14 +18690,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18666,7 +18714,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18683,7 +18731,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18693,14 +18741,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18717,7 +18765,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18734,7 +18782,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18751,7 +18799,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18768,7 +18816,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18778,14 +18826,14 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18802,7 +18850,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18819,7 +18867,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18836,7 +18884,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18846,14 +18894,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18870,7 +18918,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18887,7 +18935,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18897,14 +18945,14 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18921,7 +18969,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18938,7 +18986,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18948,14 +18996,14 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18972,7 +19020,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18982,14 +19030,14 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -19006,12 +19054,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -19023,46 +19071,46 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -19074,29 +19122,29 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -19108,46 +19156,46 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -19159,12 +19207,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -19176,7 +19224,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -19193,7 +19241,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -19210,7 +19258,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19227,7 +19275,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19244,7 +19292,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19254,14 +19302,14 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19278,7 +19326,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19288,14 +19336,14 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19312,7 +19360,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -19329,7 +19377,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -19339,14 +19387,14 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -19356,14 +19404,14 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19373,14 +19421,14 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19390,36 +19438,36 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -19431,46 +19479,46 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -19482,46 +19530,46 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -19533,12 +19581,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -19550,12 +19598,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -19567,29 +19615,29 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -19601,15 +19649,185 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
+          <t>BESTBE HOLDING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>GREEN OLEO S.p.A</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Officina Stellare S.p.A.</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Svas Biosana S.p.A.</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Energy Time S.p.A.</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>ELES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>DIADEMA CAPITAL</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Cloudia Research S.p.A.</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
           <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -19626,188 +19844,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NL0015001OJ9</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3.904000043869019</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>5.635245838316418</v>
-      </c>
-      <c r="I2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005043507</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5.21999979019165</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.681992444962531</v>
-      </c>
-      <c r="I3" t="n">
-        <v>63</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005278236</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6.184999942779541</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3.880355735171501</v>
-      </c>
-      <c r="I4" t="n">
-        <v>91</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19818,180 +19857,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Confinvest Oro S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Confinvest Oro S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DIADEMA CAPITAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ELES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>eVISO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>